--- a/商品物料.xlsx
+++ b/商品物料.xlsx
@@ -6705,7 +6705,7 @@
     <t>mini爱心镜子</t>
   </si>
   <si>
-    <t>2026秋</t>
+    <t>26秋</t>
   </si>
 </sst>
 </file>

--- a/商品物料.xlsx
+++ b/商品物料.xlsx
@@ -45788,6 +45788,9 @@
       <c r="J1002" t="s">
         <v>150</v>
       </c>
+      <c r="K1002">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L1002" etc:filterBottomFollowUsedRange="0">
